--- a/制度（せいど）.xlsx
+++ b/制度（せいど）.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="194">
   <si>
     <t>禁止</t>
   </si>
@@ -403,6 +403,12 @@
     <t>せいさく</t>
   </si>
   <si>
+    <t>刑事</t>
+  </si>
+  <si>
+    <t>けいじ</t>
+  </si>
+  <si>
     <t>規模</t>
   </si>
   <si>
@@ -464,6 +470,12 @@
   </si>
   <si>
     <t>いほう</t>
+  </si>
+  <si>
+    <t>合理</t>
+  </si>
+  <si>
+    <t>ごうり</t>
   </si>
   <si>
     <t>貧困</t>
@@ -737,6 +749,24 @@
   <si>
     <t>だいへんかく</t>
   </si>
+  <si>
+    <t>遭難</t>
+  </si>
+  <si>
+    <t>そうなん</t>
+  </si>
+  <si>
+    <t>資本</t>
+  </si>
+  <si>
+    <t>しほん</t>
+  </si>
+  <si>
+    <t>資本主義</t>
+  </si>
+  <si>
+    <t>しほんしゅぎ</t>
+  </si>
 </sst>
 </file>
 
@@ -748,7 +778,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -773,13 +803,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1236,148 +1259,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1864,7 +1887,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:H20"/>
+  <dimension ref="A2:H22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -2077,60 +2100,82 @@
       </c>
     </row>
     <row r="15" ht="18" spans="1:8">
+      <c r="A15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" t="s">
+        <v>94</v>
+      </c>
       <c r="E15" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:8">
       <c r="E16" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" ht="18" spans="5:7">
       <c r="E17" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" ht="18" spans="5:7">
       <c r="E18" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" ht="18" spans="5:7">
       <c r="E19" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" ht="18" spans="5:7">
       <c r="E20" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="5:7">
+      <c r="E21" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="5:7">
+      <c r="E22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2142,7 +2187,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G35"/>
+  <dimension ref="A2:G38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7.55555555555556" style="1" customWidth="1"/>
@@ -2155,64 +2200,64 @@
   <sheetData>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2225,240 +2270,264 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" ht="19.8" customHeight="1" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/制度（せいど）.xlsx
+++ b/制度（せいど）.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="203">
   <si>
     <t>禁止</t>
   </si>
@@ -478,6 +478,12 @@
     <t>ごうり</t>
   </si>
   <si>
+    <t>提案</t>
+  </si>
+  <si>
+    <t>ていあん</t>
+  </si>
+  <si>
     <t>貧困</t>
   </si>
   <si>
@@ -766,6 +772,27 @@
   </si>
   <si>
     <t>しほんしゅぎ</t>
+  </si>
+  <si>
+    <t>人種</t>
+  </si>
+  <si>
+    <t>じんしゅ</t>
+  </si>
+  <si>
+    <t>人目</t>
+  </si>
+  <si>
+    <t>ひとめ</t>
+  </si>
+  <si>
+    <t>（世俗的眼光）</t>
+  </si>
+  <si>
+    <t>宿命</t>
+  </si>
+  <si>
+    <t>しゅくめい</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1914,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:H22"/>
+  <dimension ref="A2:H23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -2178,6 +2205,14 @@
         <v>76</v>
       </c>
     </row>
+    <row r="23" spans="5:7">
+      <c r="E23" t="s">
+        <v>112</v>
+      </c>
+      <c r="F23" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -2187,7 +2222,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G38"/>
+  <dimension ref="A2:G41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7.55555555555556" style="1" customWidth="1"/>
@@ -2200,64 +2235,64 @@
   <sheetData>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2270,264 +2305,291 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" ht="19.8" customHeight="1" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/制度（せいど）.xlsx
+++ b/制度（せいど）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="生活（せいかつ）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="207">
   <si>
     <t>禁止</t>
   </si>
@@ -482,6 +482,18 @@
   </si>
   <si>
     <t>ていあん</t>
+  </si>
+  <si>
+    <t>法則</t>
+  </si>
+  <si>
+    <t>ほうそく</t>
+  </si>
+  <si>
+    <t>社会法則</t>
+  </si>
+  <si>
+    <t>しゃかいほうそく</t>
   </si>
   <si>
     <t>貧困</t>
@@ -1914,7 +1926,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:H23"/>
+  <dimension ref="A2:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -2211,6 +2223,22 @@
       </c>
       <c r="F23" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="5:7">
+      <c r="E24" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="5:7">
+      <c r="E25" t="s">
+        <v>116</v>
+      </c>
+      <c r="F25" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2235,64 +2263,64 @@
   <sheetData>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2305,291 +2333,291 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" ht="19.8" customHeight="1" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
